--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_la araucania.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:40</t>
+    <t xml:space="preserve">2026-09-09 22:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_la araucania.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:26</t>
+    <t xml:space="preserve">2026-09-12 19:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_la araucania.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:43</t>
+    <t xml:space="preserve">2026-09-24 00:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_la araucania.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:21</t>
+    <t xml:space="preserve">2026-09-27 22:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_la araucania.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:10</t>
+    <t xml:space="preserve">2026-10-01 20:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_la araucania.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:50</t>
+    <t xml:space="preserve">2026-10-02 13:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_la araucania.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:18</t>
+    <t xml:space="preserve">2026-10-05 07:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
